--- a/public/demo/Pedidos_Guardian_Demo.xlsx
+++ b/public/demo/Pedidos_Guardian_Demo.xlsx
@@ -424,7 +424,7 @@
         <v>PED-1001</v>
       </c>
       <c r="B2" t="str">
-        <v>TCL</v>
+        <v>Belleza Norte SA</v>
       </c>
       <c r="C2" t="str">
         <v>Shampoo Premium</v>
@@ -524,7 +524,7 @@
         <v>PED-1006</v>
       </c>
       <c r="B7" t="str">
-        <v>TCL</v>
+        <v>Belleza Norte SA</v>
       </c>
       <c r="C7" t="str">
         <v>Serum Regenerador</v>
@@ -564,7 +564,7 @@
         <v>PED-1008</v>
       </c>
       <c r="B9" t="str">
-        <v>TCL</v>
+        <v>Belleza Norte SA</v>
       </c>
       <c r="C9" t="str">
         <v>Shampoo Premium</v>
@@ -584,7 +584,7 @@
         <v>PED-1009</v>
       </c>
       <c r="B10" t="str">
-        <v>TCL</v>
+        <v>Belleza Norte SA</v>
       </c>
       <c r="C10" t="str">
         <v>Crema Hidratante</v>
@@ -744,7 +744,7 @@
         <v>PED-1017</v>
       </c>
       <c r="B18" t="str">
-        <v>TCL</v>
+        <v>Belleza Norte SA</v>
       </c>
       <c r="C18" t="str">
         <v>Serum Regenerador</v>
@@ -824,7 +824,7 @@
         <v>PED-1021</v>
       </c>
       <c r="B22" t="str">
-        <v>TCL</v>
+        <v>Belleza Norte SA</v>
       </c>
       <c r="C22" t="str">
         <v>Shampoo Premium</v>
@@ -844,7 +844,7 @@
         <v>PED-1022</v>
       </c>
       <c r="B23" t="str">
-        <v>TCL</v>
+        <v>Belleza Norte SA</v>
       </c>
       <c r="C23" t="str">
         <v>Serum Regenerador</v>
@@ -1024,7 +1024,7 @@
         <v>PED-1031</v>
       </c>
       <c r="B32" t="str">
-        <v>TCL</v>
+        <v>Belleza Norte SA</v>
       </c>
       <c r="C32" t="str">
         <v>Crema Hidratante</v>
@@ -1064,7 +1064,7 @@
         <v>PED-1033</v>
       </c>
       <c r="B34" t="str">
-        <v>TCL</v>
+        <v>Belleza Norte SA</v>
       </c>
       <c r="C34" t="str">
         <v>Shampoo Premium</v>
@@ -1084,7 +1084,7 @@
         <v>PED-1034</v>
       </c>
       <c r="B35" t="str">
-        <v>TCL</v>
+        <v>Belleza Norte SA</v>
       </c>
       <c r="C35" t="str">
         <v>Serum Regenerador</v>
@@ -1144,7 +1144,7 @@
         <v>PED-1037</v>
       </c>
       <c r="B38" t="str">
-        <v>TCL</v>
+        <v>Belleza Norte SA</v>
       </c>
       <c r="C38" t="str">
         <v>Shampoo Premium</v>
@@ -1164,7 +1164,7 @@
         <v>PED-1038</v>
       </c>
       <c r="B39" t="str">
-        <v>TCL</v>
+        <v>Belleza Norte SA</v>
       </c>
       <c r="C39" t="str">
         <v>Shampoo Premium</v>
